--- a/artfynd/A 6293-2025 artfynd.xlsx
+++ b/artfynd/A 6293-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122817511</v>
+        <v>122816814</v>
       </c>
       <c r="B2" t="n">
-        <v>79351</v>
+        <v>78503</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>498539</v>
+        <v>498410</v>
       </c>
       <c r="R2" t="n">
-        <v>6911324</v>
+        <v>6911399</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122816814</v>
+        <v>122816975</v>
       </c>
       <c r="B3" t="n">
-        <v>78499</v>
+        <v>79355</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>498410</v>
+        <v>498456</v>
       </c>
       <c r="R3" t="n">
-        <v>6911399</v>
+        <v>6911376</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122817347</v>
+        <v>122817511</v>
       </c>
       <c r="B4" t="n">
-        <v>78762</v>
+        <v>79355</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>498508</v>
+        <v>498539</v>
       </c>
       <c r="R4" t="n">
-        <v>6911438</v>
+        <v>6911324</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122818039</v>
+        <v>122818182</v>
       </c>
       <c r="B5" t="n">
-        <v>78762</v>
+        <v>79847</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,34 +1027,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
+          <t>Fröbäckstjärnarna, Fröbäckstjärnarna, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>498549</v>
+        <v>498561</v>
       </c>
       <c r="R5" t="n">
-        <v>6911033</v>
+        <v>6911205</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122816975</v>
+        <v>122817305</v>
       </c>
       <c r="B6" t="n">
-        <v>79351</v>
+        <v>79355</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>498456</v>
+        <v>498502</v>
       </c>
       <c r="R6" t="n">
-        <v>6911376</v>
+        <v>6911405</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122817660</v>
+        <v>122817580</v>
       </c>
       <c r="B7" t="n">
-        <v>56688</v>
+        <v>57478</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1247,31 +1247,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1280,10 +1280,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>498511</v>
+        <v>498562</v>
       </c>
       <c r="R7" t="n">
-        <v>6911287</v>
+        <v>6911269</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1325,7 +1325,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1352,10 +1357,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122817760</v>
+        <v>122816792</v>
       </c>
       <c r="B8" t="n">
-        <v>78499</v>
+        <v>78503</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1392,10 +1397,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>498475</v>
+        <v>498415</v>
       </c>
       <c r="R8" t="n">
-        <v>6911237</v>
+        <v>6911388</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1427,7 +1432,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1437,7 +1442,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1464,10 +1469,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122817442</v>
+        <v>122817760</v>
       </c>
       <c r="B9" t="n">
-        <v>78499</v>
+        <v>78503</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1504,10 +1509,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>498547</v>
+        <v>498475</v>
       </c>
       <c r="R9" t="n">
-        <v>6911350</v>
+        <v>6911237</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1539,7 +1544,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1549,7 +1554,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1576,10 +1581,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122817305</v>
+        <v>122818039</v>
       </c>
       <c r="B10" t="n">
-        <v>79351</v>
+        <v>78766</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1592,34 +1597,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Fröbäckstjärnarna, Fröbäckstjärnarna, Mpd</t>
+          <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>498502</v>
+        <v>498549</v>
       </c>
       <c r="R10" t="n">
-        <v>6911405</v>
+        <v>6911033</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1651,7 +1656,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1661,7 +1666,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1688,10 +1693,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122816792</v>
+        <v>122817442</v>
       </c>
       <c r="B11" t="n">
-        <v>78499</v>
+        <v>78503</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1728,10 +1733,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>498415</v>
+        <v>498547</v>
       </c>
       <c r="R11" t="n">
-        <v>6911388</v>
+        <v>6911350</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1763,7 +1768,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1773,7 +1778,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1800,10 +1805,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122817580</v>
+        <v>122817660</v>
       </c>
       <c r="B12" t="n">
-        <v>57478</v>
+        <v>56688</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1812,31 +1817,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1845,10 +1850,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>498562</v>
+        <v>498511</v>
       </c>
       <c r="R12" t="n">
-        <v>6911269</v>
+        <v>6911287</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1880,7 +1885,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1890,12 +1895,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:31</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1922,10 +1922,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122818182</v>
+        <v>122817347</v>
       </c>
       <c r="B13" t="n">
-        <v>79843</v>
+        <v>78766</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1938,21 +1938,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1962,10 +1962,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>498561</v>
+        <v>498508</v>
       </c>
       <c r="R13" t="n">
-        <v>6911205</v>
+        <v>6911438</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1997,7 +1997,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 6293-2025 artfynd.xlsx
+++ b/artfynd/A 6293-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122816814</v>
+        <v>122816975</v>
       </c>
       <c r="B2" t="n">
-        <v>78503</v>
+        <v>79355</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>498410</v>
+        <v>498456</v>
       </c>
       <c r="R2" t="n">
-        <v>6911399</v>
+        <v>6911376</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122816975</v>
+        <v>122817760</v>
       </c>
       <c r="B3" t="n">
-        <v>79355</v>
+        <v>78503</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>498456</v>
+        <v>498475</v>
       </c>
       <c r="R3" t="n">
-        <v>6911376</v>
+        <v>6911237</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122817511</v>
+        <v>122816792</v>
       </c>
       <c r="B4" t="n">
-        <v>79355</v>
+        <v>78503</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>498539</v>
+        <v>498415</v>
       </c>
       <c r="R4" t="n">
-        <v>6911324</v>
+        <v>6911388</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122818182</v>
+        <v>122817660</v>
       </c>
       <c r="B5" t="n">
-        <v>79847</v>
+        <v>56688</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,38 +1023,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Fröbäckstjärnarna, Fröbäckstjärnarna, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>498561</v>
+        <v>498511</v>
       </c>
       <c r="R5" t="n">
-        <v>6911205</v>
+        <v>6911287</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1123,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122817305</v>
+        <v>122817580</v>
       </c>
       <c r="B6" t="n">
-        <v>79355</v>
+        <v>57478</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,34 +1144,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Fröbäckstjärnarna, Fröbäckstjärnarna, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>498502</v>
+        <v>498562</v>
       </c>
       <c r="R6" t="n">
-        <v>6911405</v>
+        <v>6911269</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1218,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122817580</v>
+        <v>122817442</v>
       </c>
       <c r="B7" t="n">
-        <v>57478</v>
+        <v>78503</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,39 +1266,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Fröbäckstjärnarna, Fröbäckstjärnarna, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>498562</v>
+        <v>498547</v>
       </c>
       <c r="R7" t="n">
-        <v>6911269</v>
+        <v>6911350</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1326,11 +1336,6 @@
       <c r="AB7" t="inlineStr">
         <is>
           <t>09:31</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,10 +1362,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122816792</v>
+        <v>122818182</v>
       </c>
       <c r="B8" t="n">
-        <v>78503</v>
+        <v>79847</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1373,21 +1378,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1397,10 +1402,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>498415</v>
+        <v>498561</v>
       </c>
       <c r="R8" t="n">
-        <v>6911388</v>
+        <v>6911205</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1432,7 +1437,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1442,7 +1447,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1469,10 +1474,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122817760</v>
+        <v>122817347</v>
       </c>
       <c r="B9" t="n">
-        <v>78503</v>
+        <v>78766</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1485,21 +1490,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1509,10 +1514,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>498475</v>
+        <v>498508</v>
       </c>
       <c r="R9" t="n">
-        <v>6911237</v>
+        <v>6911438</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1544,7 +1549,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1554,7 +1559,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1581,10 +1586,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122818039</v>
+        <v>122817305</v>
       </c>
       <c r="B10" t="n">
-        <v>78766</v>
+        <v>79355</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1597,34 +1602,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
+          <t>Fröbäckstjärnarna, Fröbäckstjärnarna, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>498549</v>
+        <v>498502</v>
       </c>
       <c r="R10" t="n">
-        <v>6911033</v>
+        <v>6911405</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1656,7 +1661,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1666,7 +1671,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1693,7 +1698,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122817442</v>
+        <v>122816814</v>
       </c>
       <c r="B11" t="n">
         <v>78503</v>
@@ -1733,10 +1738,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>498547</v>
+        <v>498410</v>
       </c>
       <c r="R11" t="n">
-        <v>6911350</v>
+        <v>6911399</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1768,7 +1773,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1778,7 +1783,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1805,10 +1810,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122817660</v>
+        <v>122818039</v>
       </c>
       <c r="B12" t="n">
-        <v>56688</v>
+        <v>78766</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1817,43 +1822,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Fröbäckstjärnarna, Fröbäckstjärnarna, Mpd</t>
+          <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>498511</v>
+        <v>498549</v>
       </c>
       <c r="R12" t="n">
-        <v>6911287</v>
+        <v>6911033</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1922,10 +1922,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122817347</v>
+        <v>122817511</v>
       </c>
       <c r="B13" t="n">
-        <v>78766</v>
+        <v>79355</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1938,21 +1938,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1962,10 +1962,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>498508</v>
+        <v>498539</v>
       </c>
       <c r="R13" t="n">
-        <v>6911438</v>
+        <v>6911324</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1997,7 +1997,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 6293-2025 artfynd.xlsx
+++ b/artfynd/A 6293-2025 artfynd.xlsx
@@ -899,7 +899,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122816792</v>
+        <v>122816814</v>
       </c>
       <c r="B4" t="n">
         <v>78503</v>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>498415</v>
+        <v>498410</v>
       </c>
       <c r="R4" t="n">
-        <v>6911388</v>
+        <v>6911399</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122817660</v>
+        <v>122817580</v>
       </c>
       <c r="B5" t="n">
-        <v>56688</v>
+        <v>57478</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,31 +1023,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>498511</v>
+        <v>498562</v>
       </c>
       <c r="R5" t="n">
-        <v>6911287</v>
+        <v>6911269</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1101,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122817580</v>
+        <v>122817511</v>
       </c>
       <c r="B6" t="n">
-        <v>57478</v>
+        <v>79355</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,39 +1149,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Fröbäckstjärnarna, Fröbäckstjärnarna, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>498562</v>
+        <v>498539</v>
       </c>
       <c r="R6" t="n">
-        <v>6911269</v>
+        <v>6911324</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1219,11 +1219,6 @@
       <c r="AB6" t="inlineStr">
         <is>
           <t>09:31</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122817442</v>
+        <v>122818182</v>
       </c>
       <c r="B7" t="n">
-        <v>78503</v>
+        <v>79847</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1266,21 +1261,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1290,10 +1285,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>498547</v>
+        <v>498561</v>
       </c>
       <c r="R7" t="n">
-        <v>6911350</v>
+        <v>6911205</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1325,7 +1320,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1335,7 +1330,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1362,10 +1357,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122818182</v>
+        <v>122817660</v>
       </c>
       <c r="B8" t="n">
-        <v>79847</v>
+        <v>56688</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1374,38 +1369,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Fröbäckstjärnarna, Fröbäckstjärnarna, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>498561</v>
+        <v>498511</v>
       </c>
       <c r="R8" t="n">
-        <v>6911205</v>
+        <v>6911287</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1474,10 +1474,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122817347</v>
+        <v>122817305</v>
       </c>
       <c r="B9" t="n">
-        <v>78766</v>
+        <v>79355</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1490,21 +1490,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1514,10 +1514,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>498508</v>
+        <v>498502</v>
       </c>
       <c r="R9" t="n">
-        <v>6911438</v>
+        <v>6911405</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1586,10 +1586,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122817305</v>
+        <v>122816792</v>
       </c>
       <c r="B10" t="n">
-        <v>79355</v>
+        <v>78503</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1602,21 +1602,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1626,10 +1626,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>498502</v>
+        <v>498415</v>
       </c>
       <c r="R10" t="n">
-        <v>6911405</v>
+        <v>6911388</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1698,10 +1698,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122816814</v>
+        <v>122818039</v>
       </c>
       <c r="B11" t="n">
-        <v>78503</v>
+        <v>78766</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1714,34 +1714,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Fröbäckstjärnarna, Fröbäckstjärnarna, Mpd</t>
+          <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>498410</v>
+        <v>498549</v>
       </c>
       <c r="R11" t="n">
-        <v>6911399</v>
+        <v>6911033</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1783,7 +1783,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1810,10 +1810,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122818039</v>
+        <v>122817442</v>
       </c>
       <c r="B12" t="n">
-        <v>78766</v>
+        <v>78503</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1826,34 +1826,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
+          <t>Fröbäckstjärnarna, Fröbäckstjärnarna, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>498549</v>
+        <v>498547</v>
       </c>
       <c r="R12" t="n">
-        <v>6911033</v>
+        <v>6911350</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1885,7 +1885,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1895,7 +1895,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1922,10 +1922,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122817511</v>
+        <v>122817347</v>
       </c>
       <c r="B13" t="n">
-        <v>79355</v>
+        <v>78766</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1938,21 +1938,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1962,10 +1962,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>498539</v>
+        <v>498508</v>
       </c>
       <c r="R13" t="n">
-        <v>6911324</v>
+        <v>6911438</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1997,7 +1997,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 6293-2025 artfynd.xlsx
+++ b/artfynd/A 6293-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122816975</v>
+        <v>122818182</v>
       </c>
       <c r="B2" t="n">
-        <v>79355</v>
+        <v>79847</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229821</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>498456</v>
+        <v>498561</v>
       </c>
       <c r="R2" t="n">
-        <v>6911376</v>
+        <v>6911205</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122817760</v>
+        <v>122817347</v>
       </c>
       <c r="B3" t="n">
-        <v>78503</v>
+        <v>78766</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>498475</v>
+        <v>498508</v>
       </c>
       <c r="R3" t="n">
-        <v>6911237</v>
+        <v>6911438</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122816814</v>
+        <v>122817511</v>
       </c>
       <c r="B4" t="n">
-        <v>78503</v>
+        <v>79355</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>498410</v>
+        <v>498539</v>
       </c>
       <c r="R4" t="n">
-        <v>6911399</v>
+        <v>6911324</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122817580</v>
+        <v>122816975</v>
       </c>
       <c r="B5" t="n">
-        <v>57478</v>
+        <v>79355</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,39 +1027,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Fröbäckstjärnarna, Fröbäckstjärnarna, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>498562</v>
+        <v>498456</v>
       </c>
       <c r="R5" t="n">
-        <v>6911269</v>
+        <v>6911376</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,12 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:31</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,7 +1123,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122817511</v>
+        <v>122817305</v>
       </c>
       <c r="B6" t="n">
         <v>79355</v>
@@ -1173,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>498539</v>
+        <v>498502</v>
       </c>
       <c r="R6" t="n">
-        <v>6911324</v>
+        <v>6911405</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122818182</v>
+        <v>122817660</v>
       </c>
       <c r="B7" t="n">
-        <v>79847</v>
+        <v>56688</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1257,38 +1247,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Fröbäckstjärnarna, Fröbäckstjärnarna, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>498561</v>
+        <v>498511</v>
       </c>
       <c r="R7" t="n">
-        <v>6911205</v>
+        <v>6911287</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1357,10 +1352,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122817660</v>
+        <v>122817442</v>
       </c>
       <c r="B8" t="n">
-        <v>56688</v>
+        <v>78503</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1369,43 +1364,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Fröbäckstjärnarna, Fröbäckstjärnarna, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>498511</v>
+        <v>498547</v>
       </c>
       <c r="R8" t="n">
-        <v>6911287</v>
+        <v>6911350</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1437,7 +1427,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1447,7 +1437,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1474,10 +1464,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122817305</v>
+        <v>122817760</v>
       </c>
       <c r="B9" t="n">
-        <v>79355</v>
+        <v>78503</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1490,21 +1480,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1514,10 +1504,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>498502</v>
+        <v>498475</v>
       </c>
       <c r="R9" t="n">
-        <v>6911405</v>
+        <v>6911237</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1549,7 +1539,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1559,7 +1549,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1586,10 +1576,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122816792</v>
+        <v>122818039</v>
       </c>
       <c r="B10" t="n">
-        <v>78503</v>
+        <v>78766</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1602,34 +1592,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Fröbäckstjärnarna, Fröbäckstjärnarna, Mpd</t>
+          <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>498415</v>
+        <v>498549</v>
       </c>
       <c r="R10" t="n">
-        <v>6911388</v>
+        <v>6911033</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1661,7 +1651,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1671,7 +1661,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1698,10 +1688,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122818039</v>
+        <v>122816814</v>
       </c>
       <c r="B11" t="n">
-        <v>78766</v>
+        <v>78503</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1714,34 +1704,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
+          <t>Fröbäckstjärnarna, Fröbäckstjärnarna, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>498549</v>
+        <v>498410</v>
       </c>
       <c r="R11" t="n">
-        <v>6911033</v>
+        <v>6911399</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1773,7 +1763,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1783,7 +1773,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1810,7 +1800,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122817442</v>
+        <v>122816792</v>
       </c>
       <c r="B12" t="n">
         <v>78503</v>
@@ -1850,10 +1840,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>498547</v>
+        <v>498415</v>
       </c>
       <c r="R12" t="n">
-        <v>6911350</v>
+        <v>6911388</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1885,7 +1875,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1895,7 +1885,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1922,10 +1912,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122817347</v>
+        <v>122817580</v>
       </c>
       <c r="B13" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1938,34 +1928,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Fröbäckstjärnarna, Fröbäckstjärnarna, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>498508</v>
+        <v>498562</v>
       </c>
       <c r="R13" t="n">
-        <v>6911438</v>
+        <v>6911269</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1997,7 +1992,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2007,7 +2002,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 6293-2025 artfynd.xlsx
+++ b/artfynd/A 6293-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122818182</v>
+        <v>122818039</v>
       </c>
       <c r="B2" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Fröbäckstjärnarna, Fröbäckstjärnarna, Mpd</t>
+          <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>498561</v>
+        <v>498549</v>
       </c>
       <c r="R2" t="n">
-        <v>6911205</v>
+        <v>6911033</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122817347</v>
+        <v>122817511</v>
       </c>
       <c r="B3" t="n">
-        <v>78766</v>
+        <v>79355</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>498508</v>
+        <v>498539</v>
       </c>
       <c r="R3" t="n">
-        <v>6911438</v>
+        <v>6911324</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122817511</v>
+        <v>122817442</v>
       </c>
       <c r="B4" t="n">
-        <v>79355</v>
+        <v>78503</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>498539</v>
+        <v>498547</v>
       </c>
       <c r="R4" t="n">
-        <v>6911324</v>
+        <v>6911350</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1011,7 +1011,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122816975</v>
+        <v>122817305</v>
       </c>
       <c r="B5" t="n">
         <v>79355</v>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>498456</v>
+        <v>498502</v>
       </c>
       <c r="R5" t="n">
-        <v>6911376</v>
+        <v>6911405</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122817305</v>
+        <v>122817660</v>
       </c>
       <c r="B6" t="n">
-        <v>79355</v>
+        <v>56688</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,38 +1135,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Fröbäckstjärnarna, Fröbäckstjärnarna, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>498502</v>
+        <v>498511</v>
       </c>
       <c r="R6" t="n">
-        <v>6911405</v>
+        <v>6911287</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122817660</v>
+        <v>122816975</v>
       </c>
       <c r="B7" t="n">
-        <v>56688</v>
+        <v>79355</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1247,43 +1252,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Fröbäckstjärnarna, Fröbäckstjärnarna, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>498511</v>
+        <v>498456</v>
       </c>
       <c r="R7" t="n">
-        <v>6911287</v>
+        <v>6911376</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1352,7 +1352,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122817442</v>
+        <v>122816792</v>
       </c>
       <c r="B8" t="n">
         <v>78503</v>
@@ -1392,10 +1392,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>498547</v>
+        <v>498415</v>
       </c>
       <c r="R8" t="n">
-        <v>6911350</v>
+        <v>6911388</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1464,10 +1464,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122817760</v>
+        <v>122817347</v>
       </c>
       <c r="B9" t="n">
-        <v>78503</v>
+        <v>78766</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1480,21 +1480,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1504,10 +1504,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>498475</v>
+        <v>498508</v>
       </c>
       <c r="R9" t="n">
-        <v>6911237</v>
+        <v>6911438</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1539,7 +1539,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1549,7 +1549,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1576,10 +1576,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122818039</v>
+        <v>122817760</v>
       </c>
       <c r="B10" t="n">
-        <v>78766</v>
+        <v>78503</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1592,34 +1592,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
+          <t>Fröbäckstjärnarna, Fröbäckstjärnarna, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>498549</v>
+        <v>498475</v>
       </c>
       <c r="R10" t="n">
-        <v>6911033</v>
+        <v>6911237</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1800,10 +1800,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122816792</v>
+        <v>122818182</v>
       </c>
       <c r="B12" t="n">
-        <v>78503</v>
+        <v>79847</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1816,21 +1816,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1840,10 +1840,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>498415</v>
+        <v>498561</v>
       </c>
       <c r="R12" t="n">
-        <v>6911388</v>
+        <v>6911205</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1885,7 +1885,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 6293-2025 artfynd.xlsx
+++ b/artfynd/A 6293-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122818039</v>
+        <v>122816814</v>
       </c>
       <c r="B2" t="n">
-        <v>78766</v>
+        <v>78503</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
+          <t>Fröbäckstjärnarna, Fröbäckstjärnarna, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>498549</v>
+        <v>498410</v>
       </c>
       <c r="R2" t="n">
-        <v>6911033</v>
+        <v>6911399</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -899,7 +899,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122817442</v>
+        <v>122816792</v>
       </c>
       <c r="B4" t="n">
         <v>78503</v>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>498547</v>
+        <v>498415</v>
       </c>
       <c r="R4" t="n">
-        <v>6911350</v>
+        <v>6911388</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122817305</v>
+        <v>122818039</v>
       </c>
       <c r="B5" t="n">
-        <v>79355</v>
+        <v>78766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,34 +1027,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Fröbäckstjärnarna, Fröbäckstjärnarna, Mpd</t>
+          <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>498502</v>
+        <v>498549</v>
       </c>
       <c r="R5" t="n">
-        <v>6911405</v>
+        <v>6911033</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1240,7 +1240,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122816975</v>
+        <v>122817305</v>
       </c>
       <c r="B7" t="n">
         <v>79355</v>
@@ -1280,10 +1280,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>498456</v>
+        <v>498502</v>
       </c>
       <c r="R7" t="n">
-        <v>6911376</v>
+        <v>6911405</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1352,10 +1352,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122816792</v>
+        <v>122817347</v>
       </c>
       <c r="B8" t="n">
-        <v>78503</v>
+        <v>78766</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1368,21 +1368,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1392,10 +1392,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>498415</v>
+        <v>498508</v>
       </c>
       <c r="R8" t="n">
-        <v>6911388</v>
+        <v>6911438</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1464,10 +1464,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122817347</v>
+        <v>122817760</v>
       </c>
       <c r="B9" t="n">
-        <v>78766</v>
+        <v>78503</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1480,21 +1480,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1504,10 +1504,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>498508</v>
+        <v>498475</v>
       </c>
       <c r="R9" t="n">
-        <v>6911438</v>
+        <v>6911237</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1539,7 +1539,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1549,7 +1549,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1576,10 +1576,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122817760</v>
+        <v>122816975</v>
       </c>
       <c r="B10" t="n">
-        <v>78503</v>
+        <v>79355</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1592,21 +1592,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1616,10 +1616,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>498475</v>
+        <v>498456</v>
       </c>
       <c r="R10" t="n">
-        <v>6911237</v>
+        <v>6911376</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1651,7 +1651,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1661,7 +1661,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1688,10 +1688,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122816814</v>
+        <v>122818182</v>
       </c>
       <c r="B11" t="n">
-        <v>78503</v>
+        <v>79847</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1704,21 +1704,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1728,10 +1728,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>498410</v>
+        <v>498561</v>
       </c>
       <c r="R11" t="n">
-        <v>6911399</v>
+        <v>6911205</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1763,7 +1763,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1800,10 +1800,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122818182</v>
+        <v>122817442</v>
       </c>
       <c r="B12" t="n">
-        <v>79847</v>
+        <v>78503</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1816,21 +1816,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1840,10 +1840,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>498561</v>
+        <v>498547</v>
       </c>
       <c r="R12" t="n">
-        <v>6911205</v>
+        <v>6911350</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1885,7 +1885,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 6293-2025 artfynd.xlsx
+++ b/artfynd/A 6293-2025 artfynd.xlsx
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122816792</v>
+        <v>122818039</v>
       </c>
       <c r="B4" t="n">
-        <v>78503</v>
+        <v>78766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,34 +915,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Fröbäckstjärnarna, Fröbäckstjärnarna, Mpd</t>
+          <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>498415</v>
+        <v>498549</v>
       </c>
       <c r="R4" t="n">
-        <v>6911388</v>
+        <v>6911033</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122818039</v>
+        <v>122816792</v>
       </c>
       <c r="B5" t="n">
-        <v>78766</v>
+        <v>78503</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,34 +1027,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
+          <t>Fröbäckstjärnarna, Fröbäckstjärnarna, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>498549</v>
+        <v>498415</v>
       </c>
       <c r="R5" t="n">
-        <v>6911033</v>
+        <v>6911388</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 6293-2025 artfynd.xlsx
+++ b/artfynd/A 6293-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122816814</v>
+        <v>122817442</v>
       </c>
       <c r="B2" t="n">
         <v>78503</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>498410</v>
+        <v>498547</v>
       </c>
       <c r="R2" t="n">
-        <v>6911399</v>
+        <v>6911350</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122817511</v>
+        <v>122818182</v>
       </c>
       <c r="B3" t="n">
-        <v>79355</v>
+        <v>79847</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>498539</v>
+        <v>498561</v>
       </c>
       <c r="R3" t="n">
-        <v>6911324</v>
+        <v>6911205</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122818039</v>
+        <v>122816975</v>
       </c>
       <c r="B4" t="n">
-        <v>78766</v>
+        <v>79355</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,34 +915,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
+          <t>Fröbäckstjärnarna, Fröbäckstjärnarna, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>498549</v>
+        <v>498456</v>
       </c>
       <c r="R4" t="n">
-        <v>6911033</v>
+        <v>6911376</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122816792</v>
+        <v>122818039</v>
       </c>
       <c r="B5" t="n">
-        <v>78503</v>
+        <v>78766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,34 +1027,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Fröbäckstjärnarna, Fröbäckstjärnarna, Mpd</t>
+          <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>498415</v>
+        <v>498549</v>
       </c>
       <c r="R5" t="n">
-        <v>6911388</v>
+        <v>6911033</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122817660</v>
+        <v>122816792</v>
       </c>
       <c r="B6" t="n">
-        <v>56688</v>
+        <v>78503</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,43 +1135,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Fröbäckstjärnarna, Fröbäckstjärnarna, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>498511</v>
+        <v>498415</v>
       </c>
       <c r="R6" t="n">
-        <v>6911287</v>
+        <v>6911388</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122817305</v>
+        <v>122817660</v>
       </c>
       <c r="B7" t="n">
-        <v>79355</v>
+        <v>56688</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1252,38 +1247,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Fröbäckstjärnarna, Fröbäckstjärnarna, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>498502</v>
+        <v>498511</v>
       </c>
       <c r="R7" t="n">
-        <v>6911405</v>
+        <v>6911287</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1352,10 +1352,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122817347</v>
+        <v>122817511</v>
       </c>
       <c r="B8" t="n">
-        <v>78766</v>
+        <v>79355</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1368,21 +1368,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1392,10 +1392,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>498508</v>
+        <v>498539</v>
       </c>
       <c r="R8" t="n">
-        <v>6911438</v>
+        <v>6911324</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1464,10 +1464,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122817760</v>
+        <v>122817347</v>
       </c>
       <c r="B9" t="n">
-        <v>78503</v>
+        <v>78766</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1480,21 +1480,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1504,10 +1504,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>498475</v>
+        <v>498508</v>
       </c>
       <c r="R9" t="n">
-        <v>6911237</v>
+        <v>6911438</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1539,7 +1539,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1549,7 +1549,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1576,7 +1576,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122816975</v>
+        <v>122817305</v>
       </c>
       <c r="B10" t="n">
         <v>79355</v>
@@ -1616,10 +1616,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>498456</v>
+        <v>498502</v>
       </c>
       <c r="R10" t="n">
-        <v>6911376</v>
+        <v>6911405</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1688,10 +1688,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122818182</v>
+        <v>122816814</v>
       </c>
       <c r="B11" t="n">
-        <v>79847</v>
+        <v>78503</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1704,21 +1704,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1728,10 +1728,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>498561</v>
+        <v>498410</v>
       </c>
       <c r="R11" t="n">
-        <v>6911205</v>
+        <v>6911399</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1763,7 +1763,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1800,7 +1800,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122817442</v>
+        <v>122817760</v>
       </c>
       <c r="B12" t="n">
         <v>78503</v>
@@ -1840,10 +1840,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>498547</v>
+        <v>498475</v>
       </c>
       <c r="R12" t="n">
-        <v>6911350</v>
+        <v>6911237</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1885,7 +1885,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 6293-2025 artfynd.xlsx
+++ b/artfynd/A 6293-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122817442</v>
+        <v>122817347</v>
       </c>
       <c r="B2" t="n">
-        <v>78503</v>
+        <v>78766</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>498547</v>
+        <v>498508</v>
       </c>
       <c r="R2" t="n">
-        <v>6911350</v>
+        <v>6911438</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122816975</v>
+        <v>122817442</v>
       </c>
       <c r="B4" t="n">
-        <v>79355</v>
+        <v>78503</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>498456</v>
+        <v>498547</v>
       </c>
       <c r="R4" t="n">
-        <v>6911376</v>
+        <v>6911350</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122818039</v>
+        <v>122816975</v>
       </c>
       <c r="B5" t="n">
-        <v>78766</v>
+        <v>79355</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,34 +1027,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
+          <t>Fröbäckstjärnarna, Fröbäckstjärnarna, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>498549</v>
+        <v>498456</v>
       </c>
       <c r="R5" t="n">
-        <v>6911033</v>
+        <v>6911376</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,7 +1123,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122816792</v>
+        <v>122816814</v>
       </c>
       <c r="B6" t="n">
         <v>78503</v>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>498415</v>
+        <v>498410</v>
       </c>
       <c r="R6" t="n">
-        <v>6911388</v>
+        <v>6911399</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122817660</v>
+        <v>122817305</v>
       </c>
       <c r="B7" t="n">
-        <v>56688</v>
+        <v>79355</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1247,43 +1247,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Fröbäckstjärnarna, Fröbäckstjärnarna, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>498511</v>
+        <v>498502</v>
       </c>
       <c r="R7" t="n">
-        <v>6911287</v>
+        <v>6911405</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1315,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1325,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1464,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122817347</v>
+        <v>122816792</v>
       </c>
       <c r="B9" t="n">
-        <v>78766</v>
+        <v>78503</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1480,21 +1475,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1504,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>498508</v>
+        <v>498415</v>
       </c>
       <c r="R9" t="n">
-        <v>6911438</v>
+        <v>6911388</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1576,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122817305</v>
+        <v>122817760</v>
       </c>
       <c r="B10" t="n">
-        <v>79355</v>
+        <v>78503</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1592,21 +1587,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1616,10 +1611,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>498502</v>
+        <v>498475</v>
       </c>
       <c r="R10" t="n">
-        <v>6911405</v>
+        <v>6911237</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1651,7 +1646,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1661,7 +1656,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1688,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122816814</v>
+        <v>122817660</v>
       </c>
       <c r="B11" t="n">
-        <v>78503</v>
+        <v>56688</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1700,38 +1695,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Fröbäckstjärnarna, Fröbäckstjärnarna, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>498410</v>
+        <v>498511</v>
       </c>
       <c r="R11" t="n">
-        <v>6911399</v>
+        <v>6911287</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1763,7 +1763,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1800,10 +1800,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122817760</v>
+        <v>122818039</v>
       </c>
       <c r="B12" t="n">
-        <v>78503</v>
+        <v>78766</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1816,34 +1816,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Fröbäckstjärnarna, Fröbäckstjärnarna, Mpd</t>
+          <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>498475</v>
+        <v>498549</v>
       </c>
       <c r="R12" t="n">
-        <v>6911237</v>
+        <v>6911033</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 6293-2025 artfynd.xlsx
+++ b/artfynd/A 6293-2025 artfynd.xlsx
@@ -1683,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122817660</v>
+        <v>122818039</v>
       </c>
       <c r="B11" t="n">
-        <v>56688</v>
+        <v>78766</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1695,43 +1695,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Fröbäckstjärnarna, Fröbäckstjärnarna, Mpd</t>
+          <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>498511</v>
+        <v>498549</v>
       </c>
       <c r="R11" t="n">
-        <v>6911287</v>
+        <v>6911033</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1800,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122818039</v>
+        <v>122817660</v>
       </c>
       <c r="B12" t="n">
-        <v>78766</v>
+        <v>56688</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1812,38 +1807,43 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
+          <t>Fröbäckstjärnarna, Fröbäckstjärnarna, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>498549</v>
+        <v>498511</v>
       </c>
       <c r="R12" t="n">
-        <v>6911033</v>
+        <v>6911287</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 6293-2025 artfynd.xlsx
+++ b/artfynd/A 6293-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122817347</v>
+        <v>122816975</v>
       </c>
       <c r="B2" t="n">
-        <v>78766</v>
+        <v>79358</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>498508</v>
+        <v>498456</v>
       </c>
       <c r="R2" t="n">
-        <v>6911438</v>
+        <v>6911376</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -790,7 +790,7 @@
         <v>122818182</v>
       </c>
       <c r="B3" t="n">
-        <v>79847</v>
+        <v>79850</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122817442</v>
+        <v>122818039</v>
       </c>
       <c r="B4" t="n">
-        <v>78503</v>
+        <v>78769</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,34 +915,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Fröbäckstjärnarna, Fröbäckstjärnarna, Mpd</t>
+          <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>498547</v>
+        <v>498549</v>
       </c>
       <c r="R4" t="n">
-        <v>6911350</v>
+        <v>6911033</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122816975</v>
+        <v>122817442</v>
       </c>
       <c r="B5" t="n">
-        <v>79355</v>
+        <v>78506</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>498456</v>
+        <v>498547</v>
       </c>
       <c r="R5" t="n">
-        <v>6911376</v>
+        <v>6911350</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122816814</v>
+        <v>122817511</v>
       </c>
       <c r="B6" t="n">
-        <v>78503</v>
+        <v>79358</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,21 +1139,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>498410</v>
+        <v>498539</v>
       </c>
       <c r="R6" t="n">
-        <v>6911399</v>
+        <v>6911324</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122817305</v>
+        <v>122817347</v>
       </c>
       <c r="B7" t="n">
-        <v>79355</v>
+        <v>78769</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,21 +1251,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>498502</v>
+        <v>498508</v>
       </c>
       <c r="R7" t="n">
-        <v>6911405</v>
+        <v>6911438</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122817511</v>
+        <v>122817660</v>
       </c>
       <c r="B8" t="n">
-        <v>79355</v>
+        <v>56691</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1359,38 +1359,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Fröbäckstjärnarna, Fröbäckstjärnarna, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>498539</v>
+        <v>498511</v>
       </c>
       <c r="R8" t="n">
-        <v>6911324</v>
+        <v>6911287</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1422,7 +1427,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1437,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,10 +1464,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122816792</v>
+        <v>122817305</v>
       </c>
       <c r="B9" t="n">
-        <v>78503</v>
+        <v>79358</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1475,21 +1480,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1504,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>498415</v>
+        <v>498502</v>
       </c>
       <c r="R9" t="n">
-        <v>6911388</v>
+        <v>6911405</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1571,10 +1576,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122817760</v>
+        <v>122816814</v>
       </c>
       <c r="B10" t="n">
-        <v>78503</v>
+        <v>78506</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1611,10 +1616,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>498475</v>
+        <v>498410</v>
       </c>
       <c r="R10" t="n">
-        <v>6911237</v>
+        <v>6911399</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1646,7 +1651,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1656,7 +1661,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,10 +1688,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122818039</v>
+        <v>122817760</v>
       </c>
       <c r="B11" t="n">
-        <v>78766</v>
+        <v>78506</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1699,34 +1704,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
+          <t>Fröbäckstjärnarna, Fröbäckstjärnarna, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>498549</v>
+        <v>498475</v>
       </c>
       <c r="R11" t="n">
-        <v>6911033</v>
+        <v>6911237</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1795,10 +1800,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122817660</v>
+        <v>122816792</v>
       </c>
       <c r="B12" t="n">
-        <v>56688</v>
+        <v>78506</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1807,43 +1812,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Fröbäckstjärnarna, Fröbäckstjärnarna, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>498511</v>
+        <v>498415</v>
       </c>
       <c r="R12" t="n">
-        <v>6911287</v>
+        <v>6911388</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1885,7 +1885,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1915,7 +1915,7 @@
         <v>122817580</v>
       </c>
       <c r="B13" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>

--- a/artfynd/A 6293-2025 artfynd.xlsx
+++ b/artfynd/A 6293-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122816975</v>
+        <v>122817347</v>
       </c>
       <c r="B2" t="n">
-        <v>79358</v>
+        <v>78771</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>498456</v>
+        <v>498508</v>
       </c>
       <c r="R2" t="n">
-        <v>6911376</v>
+        <v>6911438</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122818182</v>
+        <v>122817305</v>
       </c>
       <c r="B3" t="n">
-        <v>79850</v>
+        <v>79360</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>229821</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>498561</v>
+        <v>498502</v>
       </c>
       <c r="R3" t="n">
-        <v>6911205</v>
+        <v>6911405</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122818039</v>
+        <v>122817760</v>
       </c>
       <c r="B4" t="n">
-        <v>78769</v>
+        <v>78508</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,34 +915,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
+          <t>Fröbäckstjärnarna, Fröbäckstjärnarna, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>498549</v>
+        <v>498475</v>
       </c>
       <c r="R4" t="n">
-        <v>6911033</v>
+        <v>6911237</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122817442</v>
+        <v>122817511</v>
       </c>
       <c r="B5" t="n">
-        <v>78506</v>
+        <v>79360</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>498547</v>
+        <v>498539</v>
       </c>
       <c r="R5" t="n">
-        <v>6911350</v>
+        <v>6911324</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122817511</v>
+        <v>122817660</v>
       </c>
       <c r="B6" t="n">
-        <v>79358</v>
+        <v>56691</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,38 +1135,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Fröbäckstjärnarna, Fröbäckstjärnarna, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>498539</v>
+        <v>498511</v>
       </c>
       <c r="R6" t="n">
-        <v>6911324</v>
+        <v>6911287</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122817347</v>
+        <v>122817442</v>
       </c>
       <c r="B7" t="n">
-        <v>78769</v>
+        <v>78508</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,21 +1256,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1280,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>498508</v>
+        <v>498547</v>
       </c>
       <c r="R7" t="n">
-        <v>6911438</v>
+        <v>6911350</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1310,7 +1315,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1325,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,10 +1352,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122817660</v>
+        <v>122818182</v>
       </c>
       <c r="B8" t="n">
-        <v>56691</v>
+        <v>79852</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1359,43 +1364,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Fröbäckstjärnarna, Fröbäckstjärnarna, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>498511</v>
+        <v>498561</v>
       </c>
       <c r="R8" t="n">
-        <v>6911287</v>
+        <v>6911205</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1464,10 +1464,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122817305</v>
+        <v>122818039</v>
       </c>
       <c r="B9" t="n">
-        <v>79358</v>
+        <v>78771</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1480,34 +1480,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Fröbäckstjärnarna, Fröbäckstjärnarna, Mpd</t>
+          <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>498502</v>
+        <v>498549</v>
       </c>
       <c r="R9" t="n">
-        <v>6911405</v>
+        <v>6911033</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1539,7 +1539,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1549,7 +1549,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1576,10 +1576,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122816814</v>
+        <v>122816792</v>
       </c>
       <c r="B10" t="n">
-        <v>78506</v>
+        <v>78508</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1616,10 +1616,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>498410</v>
+        <v>498415</v>
       </c>
       <c r="R10" t="n">
-        <v>6911399</v>
+        <v>6911388</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1688,10 +1688,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122817760</v>
+        <v>122816975</v>
       </c>
       <c r="B11" t="n">
-        <v>78506</v>
+        <v>79360</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1704,21 +1704,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1728,10 +1728,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>498475</v>
+        <v>498456</v>
       </c>
       <c r="R11" t="n">
-        <v>6911237</v>
+        <v>6911376</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1763,7 +1763,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1800,10 +1800,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122816792</v>
+        <v>122816814</v>
       </c>
       <c r="B12" t="n">
-        <v>78506</v>
+        <v>78508</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1840,10 +1840,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>498415</v>
+        <v>498410</v>
       </c>
       <c r="R12" t="n">
-        <v>6911388</v>
+        <v>6911399</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 6293-2025 artfynd.xlsx
+++ b/artfynd/A 6293-2025 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122817305</v>
+        <v>122817760</v>
       </c>
       <c r="B3" t="n">
-        <v>79360</v>
+        <v>78508</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>498502</v>
+        <v>498475</v>
       </c>
       <c r="R3" t="n">
-        <v>6911405</v>
+        <v>6911237</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122817760</v>
+        <v>122817305</v>
       </c>
       <c r="B4" t="n">
-        <v>78508</v>
+        <v>79360</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>498475</v>
+        <v>498502</v>
       </c>
       <c r="R4" t="n">
-        <v>6911237</v>
+        <v>6911405</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 6293-2025 artfynd.xlsx
+++ b/artfynd/A 6293-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122817347</v>
+        <v>122818182</v>
       </c>
       <c r="B2" t="n">
-        <v>78771</v>
+        <v>79853</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>498508</v>
+        <v>498561</v>
       </c>
       <c r="R2" t="n">
-        <v>6911438</v>
+        <v>6911205</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122817760</v>
+        <v>122817511</v>
       </c>
       <c r="B3" t="n">
-        <v>78508</v>
+        <v>79361</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>498475</v>
+        <v>498539</v>
       </c>
       <c r="R3" t="n">
-        <v>6911237</v>
+        <v>6911324</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122817305</v>
+        <v>122816975</v>
       </c>
       <c r="B4" t="n">
-        <v>79360</v>
+        <v>79361</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>498502</v>
+        <v>498456</v>
       </c>
       <c r="R4" t="n">
-        <v>6911405</v>
+        <v>6911376</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122817511</v>
+        <v>122818039</v>
       </c>
       <c r="B5" t="n">
-        <v>79360</v>
+        <v>78772</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,34 +1027,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Fröbäckstjärnarna, Fröbäckstjärnarna, Mpd</t>
+          <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>498539</v>
+        <v>498549</v>
       </c>
       <c r="R5" t="n">
-        <v>6911324</v>
+        <v>6911033</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122817660</v>
+        <v>122816814</v>
       </c>
       <c r="B6" t="n">
-        <v>56691</v>
+        <v>78509</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,43 +1135,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Fröbäckstjärnarna, Fröbäckstjärnarna, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>498511</v>
+        <v>498410</v>
       </c>
       <c r="R6" t="n">
-        <v>6911287</v>
+        <v>6911399</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1243,7 +1238,7 @@
         <v>122817442</v>
       </c>
       <c r="B7" t="n">
-        <v>78508</v>
+        <v>78509</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1352,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122818182</v>
+        <v>122816792</v>
       </c>
       <c r="B8" t="n">
-        <v>79852</v>
+        <v>78509</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1368,21 +1363,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1392,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>498561</v>
+        <v>498415</v>
       </c>
       <c r="R8" t="n">
-        <v>6911205</v>
+        <v>6911388</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1427,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1437,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1464,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122818039</v>
+        <v>122817660</v>
       </c>
       <c r="B9" t="n">
-        <v>78771</v>
+        <v>56691</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1476,38 +1471,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
+          <t>Fröbäckstjärnarna, Fröbäckstjärnarna, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>498549</v>
+        <v>498511</v>
       </c>
       <c r="R9" t="n">
-        <v>6911033</v>
+        <v>6911287</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1576,10 +1576,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122816792</v>
+        <v>122817347</v>
       </c>
       <c r="B10" t="n">
-        <v>78508</v>
+        <v>78772</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1592,21 +1592,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1616,10 +1616,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>498415</v>
+        <v>498508</v>
       </c>
       <c r="R10" t="n">
-        <v>6911388</v>
+        <v>6911438</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1688,10 +1688,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122816975</v>
+        <v>122817305</v>
       </c>
       <c r="B11" t="n">
-        <v>79360</v>
+        <v>79361</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1728,10 +1728,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>498456</v>
+        <v>498502</v>
       </c>
       <c r="R11" t="n">
-        <v>6911376</v>
+        <v>6911405</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1800,10 +1800,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122816814</v>
+        <v>122817760</v>
       </c>
       <c r="B12" t="n">
-        <v>78508</v>
+        <v>78509</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1840,10 +1840,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>498410</v>
+        <v>498475</v>
       </c>
       <c r="R12" t="n">
-        <v>6911399</v>
+        <v>6911237</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1885,7 +1885,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 6293-2025 artfynd.xlsx
+++ b/artfynd/A 6293-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122818182</v>
+        <v>122816814</v>
       </c>
       <c r="B2" t="n">
-        <v>79853</v>
+        <v>78512</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>498561</v>
+        <v>498410</v>
       </c>
       <c r="R2" t="n">
-        <v>6911205</v>
+        <v>6911399</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122817511</v>
+        <v>122817442</v>
       </c>
       <c r="B3" t="n">
-        <v>79361</v>
+        <v>78512</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>498539</v>
+        <v>498547</v>
       </c>
       <c r="R3" t="n">
-        <v>6911324</v>
+        <v>6911350</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122816975</v>
+        <v>122817305</v>
       </c>
       <c r="B4" t="n">
-        <v>79361</v>
+        <v>79364</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>498456</v>
+        <v>498502</v>
       </c>
       <c r="R4" t="n">
-        <v>6911376</v>
+        <v>6911405</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122818039</v>
+        <v>122816975</v>
       </c>
       <c r="B5" t="n">
-        <v>78772</v>
+        <v>79364</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,34 +1027,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
+          <t>Fröbäckstjärnarna, Fröbäckstjärnarna, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>498549</v>
+        <v>498456</v>
       </c>
       <c r="R5" t="n">
-        <v>6911033</v>
+        <v>6911376</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122816814</v>
+        <v>122817347</v>
       </c>
       <c r="B6" t="n">
-        <v>78509</v>
+        <v>78775</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,21 +1139,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>498410</v>
+        <v>498508</v>
       </c>
       <c r="R6" t="n">
-        <v>6911399</v>
+        <v>6911438</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122817442</v>
+        <v>122817760</v>
       </c>
       <c r="B7" t="n">
-        <v>78509</v>
+        <v>78512</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>498547</v>
+        <v>498475</v>
       </c>
       <c r="R7" t="n">
-        <v>6911350</v>
+        <v>6911237</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122816792</v>
+        <v>122818039</v>
       </c>
       <c r="B8" t="n">
-        <v>78509</v>
+        <v>78775</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1363,34 +1363,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Fröbäckstjärnarna, Fröbäckstjärnarna, Mpd</t>
+          <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>498415</v>
+        <v>498549</v>
       </c>
       <c r="R8" t="n">
-        <v>6911388</v>
+        <v>6911033</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1576,10 +1576,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122817347</v>
+        <v>122816792</v>
       </c>
       <c r="B10" t="n">
-        <v>78772</v>
+        <v>78512</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1592,21 +1592,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1616,10 +1616,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>498508</v>
+        <v>498415</v>
       </c>
       <c r="R10" t="n">
-        <v>6911438</v>
+        <v>6911388</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1688,10 +1688,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122817305</v>
+        <v>122817511</v>
       </c>
       <c r="B11" t="n">
-        <v>79361</v>
+        <v>79364</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1728,10 +1728,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>498502</v>
+        <v>498539</v>
       </c>
       <c r="R11" t="n">
-        <v>6911405</v>
+        <v>6911324</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1763,7 +1763,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1800,10 +1800,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122817760</v>
+        <v>122818182</v>
       </c>
       <c r="B12" t="n">
-        <v>78509</v>
+        <v>79856</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1816,21 +1816,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1840,10 +1840,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>498475</v>
+        <v>498561</v>
       </c>
       <c r="R12" t="n">
-        <v>6911237</v>
+        <v>6911205</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 6293-2025 artfynd.xlsx
+++ b/artfynd/A 6293-2025 artfynd.xlsx
@@ -1915,7 +1915,7 @@
         <v>122817580</v>
       </c>
       <c r="B13" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
